--- a/resources/spawn_world_entity.xlsx
+++ b/resources/spawn_world_entity.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="28680" yWindow="-1095" windowWidth="29040" windowHeight="15720" tabRatio="600" firstSheet="0" activeTab="1" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="CONFIG" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="SpawnWorldEntity" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="CONFIG" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="SpawnWorldEntity" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="162913" fullCalcOnLoad="1"/>
@@ -885,7 +885,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P69"/>
+  <dimension ref="A1:P70"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="14.25"/>
   <cols>
     <col width="15.875" customWidth="1" style="16" min="1" max="1"/>
@@ -1371,7 +1371,7 @@
       </c>
       <c r="K10" s="9" t="inlineStr">
         <is>
-          <t> </t>
+          <t xml:space="preserve"> </t>
         </is>
       </c>
     </row>
@@ -3730,37 +3730,33 @@
       <c r="P67" s="10" t="n"/>
     </row>
     <row r="68">
-      <c r="A68" s="10" t="n"/>
-      <c r="B68" s="10" t="inlineStr">
-        <is>
-          <t>required:1</t>
-        </is>
+      <c r="A68" s="10" t="n">
+        <v>10013111016</v>
+      </c>
+      <c r="B68" s="10" t="n">
+        <v>10008</v>
       </c>
       <c r="C68" s="10" t="n"/>
-      <c r="D68" s="10" t="inlineStr">
-        <is>
-          <t>required:1</t>
-        </is>
-      </c>
-      <c r="E68" s="10" t="n"/>
-      <c r="F68" s="10" t="inlineStr">
-        <is>
-          <t>required:1</t>
-        </is>
-      </c>
-      <c r="G68" s="10" t="inlineStr">
-        <is>
-          <t>required:1</t>
-        </is>
-      </c>
-      <c r="H68" s="10" t="n"/>
+      <c r="D68" s="10" t="n">
+        <v>10013112016</v>
+      </c>
+      <c r="E68" s="10" t="inlineStr">
+        <is>
+          <t>铁匠老张</t>
+        </is>
+      </c>
+      <c r="F68" s="10" t="n"/>
+      <c r="G68" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="H68" s="10" t="inlineStr">
+        <is>
+          <t>(60,0,30)</t>
+        </is>
+      </c>
       <c r="I68" s="10" t="n"/>
       <c r="J68" s="10" t="n"/>
-      <c r="K68" s="10" t="inlineStr">
-        <is>
-          <t>required:1</t>
-        </is>
-      </c>
+      <c r="K68" s="10" t="n"/>
       <c r="L68" s="10" t="n"/>
       <c r="M68" s="10" t="n"/>
       <c r="N68" s="10" t="n"/>
@@ -3769,23 +3765,61 @@
     </row>
     <row r="69">
       <c r="A69" s="10" t="n"/>
-      <c r="B69" s="10" t="n"/>
+      <c r="B69" s="10" t="inlineStr">
+        <is>
+          <t>required:1</t>
+        </is>
+      </c>
       <c r="C69" s="10" t="n"/>
-      <c r="D69" s="10" t="n"/>
+      <c r="D69" s="10" t="inlineStr">
+        <is>
+          <t>required:1</t>
+        </is>
+      </c>
       <c r="E69" s="10" t="n"/>
-      <c r="F69" s="10" t="n"/>
-      <c r="G69" s="10" t="n"/>
+      <c r="F69" s="10" t="inlineStr">
+        <is>
+          <t>required:1</t>
+        </is>
+      </c>
+      <c r="G69" s="10" t="inlineStr">
+        <is>
+          <t>required:1</t>
+        </is>
+      </c>
       <c r="H69" s="10" t="n"/>
       <c r="I69" s="10" t="n"/>
       <c r="J69" s="10" t="n"/>
-      <c r="K69" s="10" t="n"/>
-      <c r="L69" s="10" t="n">
-        <v>0</v>
-      </c>
+      <c r="K69" s="10" t="inlineStr">
+        <is>
+          <t>required:1</t>
+        </is>
+      </c>
+      <c r="L69" s="10" t="n"/>
       <c r="M69" s="10" t="n"/>
       <c r="N69" s="10" t="n"/>
       <c r="O69" s="10" t="n"/>
       <c r="P69" s="10" t="n"/>
+    </row>
+    <row r="70">
+      <c r="A70" s="10" t="n"/>
+      <c r="B70" s="10" t="n"/>
+      <c r="C70" s="10" t="n"/>
+      <c r="D70" s="10" t="n"/>
+      <c r="E70" s="10" t="n"/>
+      <c r="F70" s="10" t="n"/>
+      <c r="G70" s="10" t="n"/>
+      <c r="H70" s="10" t="n"/>
+      <c r="I70" s="10" t="n"/>
+      <c r="J70" s="10" t="n"/>
+      <c r="K70" s="10" t="n"/>
+      <c r="L70" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="M70" s="10" t="n"/>
+      <c r="N70" s="10" t="n"/>
+      <c r="O70" s="10" t="n"/>
+      <c r="P70" s="10" t="n"/>
     </row>
   </sheetData>
   <conditionalFormatting sqref="A51:A54 A56:A64">
